--- a/Forrás/2-14be.xlsx
+++ b/Forrás/2-14be.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20414"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\boros.bence\source\repos\IskolaAPI\Forrás\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C5997AF-A8AC-48B0-BED4-33F6467FCC74}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF3D85F2-1839-4E1C-86D4-6F4AD2BCC5DF}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{5EC9E8D7-03B0-4851-8BB8-D6719EE99A19}"/>
   </bookViews>
@@ -25,115 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
-  <si>
-    <t>Takács András</t>
-  </si>
-  <si>
-    <t>bsze3takand@vasvari.org</t>
-  </si>
-  <si>
-    <t>Pécsi Bianka</t>
-  </si>
-  <si>
-    <t>bsze3pecbia@vasvari.org</t>
-  </si>
-  <si>
-    <t>Erdélyi Dávid</t>
-  </si>
-  <si>
-    <t>bsze3erddav@vasvari.org</t>
-  </si>
-  <si>
-    <t>Molnár Edit</t>
-  </si>
-  <si>
-    <t>molnar.edit@vasvari.org</t>
-  </si>
-  <si>
-    <t>Wittmann Gyula</t>
-  </si>
-  <si>
-    <t>csze2witgyu@vasvari.org</t>
-  </si>
-  <si>
-    <t>Simon Gábor</t>
-  </si>
-  <si>
-    <t>bsze3simgab@vasvari.org</t>
-  </si>
-  <si>
-    <t>Varga Gábor</t>
-  </si>
-  <si>
-    <t>bsze3vargab@vasvari.org</t>
-  </si>
-  <si>
-    <t>Csóti István</t>
-  </si>
-  <si>
-    <t>bsze3csoist@vasvari.org</t>
-  </si>
-  <si>
-    <t>Kovács József Miklós</t>
-  </si>
-  <si>
-    <t>bsze3kovjoz@vasvari.org</t>
-  </si>
-  <si>
-    <t>Huszka Leila Renáta</t>
-  </si>
-  <si>
-    <t>bsze3huslei@vasvari.org</t>
-  </si>
-  <si>
-    <t>Lajkó Levente</t>
-  </si>
-  <si>
-    <t>bsze3lajlev@vasvari.org</t>
-  </si>
-  <si>
-    <t>Székely Levente</t>
-  </si>
-  <si>
-    <t>bsze3szelev@vasvari.org</t>
-  </si>
-  <si>
-    <t>Kopincu Máté</t>
-  </si>
-  <si>
-    <t>bsze3kopmat@vasvari.org</t>
-  </si>
-  <si>
-    <t>Márkus Netti Teodóra</t>
-  </si>
-  <si>
-    <t>bsze3marnet@vasvari.org</t>
-  </si>
-  <si>
-    <t>Horváth Péter</t>
-  </si>
-  <si>
-    <t>bsze3horpet@vasvari.org</t>
-  </si>
-  <si>
-    <t>Guba Viktor</t>
-  </si>
-  <si>
-    <t>bsze3gubvik@vasvari.org</t>
-  </si>
-  <si>
-    <t>Grezsa Zoltán Gábor</t>
-  </si>
-  <si>
-    <t>bsze3grezol@vasvari.org</t>
-  </si>
-  <si>
-    <t>Töröcsik Ákos</t>
-  </si>
-  <si>
-    <t>bsze3torako@vasvari.org</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="56">
   <si>
     <t>Név</t>
   </si>
@@ -145,6 +37,162 @@
   </si>
   <si>
     <t>#</t>
+  </si>
+  <si>
+    <t>Szűcs Ágnes</t>
+  </si>
+  <si>
+    <t>sze4szuagn@vasvari.org</t>
+  </si>
+  <si>
+    <t>Becsei Ákos</t>
+  </si>
+  <si>
+    <t>sze4becako@vasvari.org</t>
+  </si>
+  <si>
+    <t>Dombi Balázs</t>
+  </si>
+  <si>
+    <t>sze4dombal@vasvari.org</t>
+  </si>
+  <si>
+    <t>Posztós Balázs</t>
+  </si>
+  <si>
+    <t>sze4posbal@vasvari.org</t>
+  </si>
+  <si>
+    <t>Bodor Bálint</t>
+  </si>
+  <si>
+    <t>sze4bodbal@vasvari.org</t>
+  </si>
+  <si>
+    <t>Kiss Bálint</t>
+  </si>
+  <si>
+    <t>sze4kisbal@vasvari.org</t>
+  </si>
+  <si>
+    <t>Batki Beatrix</t>
+  </si>
+  <si>
+    <t>sze4batbea@vasvari.org</t>
+  </si>
+  <si>
+    <t>Csehók Csaba</t>
+  </si>
+  <si>
+    <t>sze4csecsa@vasvari.org</t>
+  </si>
+  <si>
+    <t>Derda Dominik</t>
+  </si>
+  <si>
+    <t>sze4derdom@vasvari.org</t>
+  </si>
+  <si>
+    <t>Kali Endre Attila</t>
+  </si>
+  <si>
+    <t>sze4kalend@vasvari.org</t>
+  </si>
+  <si>
+    <t>Lajkó Gábor Alexander</t>
+  </si>
+  <si>
+    <t>sz4lajgab@vasvari.org</t>
+  </si>
+  <si>
+    <t>Szabó Kata</t>
+  </si>
+  <si>
+    <t>sze4szakat@vasvari.org</t>
+  </si>
+  <si>
+    <t>Kőműves Kornélia</t>
+  </si>
+  <si>
+    <t>sze4komkor@vasvari.org</t>
+  </si>
+  <si>
+    <t>Szabó Levente János</t>
+  </si>
+  <si>
+    <t>sze4szalev@vasvari.org</t>
+  </si>
+  <si>
+    <t>Bálint László Adrián</t>
+  </si>
+  <si>
+    <t>sze4ballas@vasvari.org</t>
+  </si>
+  <si>
+    <t>Kling Martin</t>
+  </si>
+  <si>
+    <t>sze4klimar@vasvari.org</t>
+  </si>
+  <si>
+    <t>Sánta Máté</t>
+  </si>
+  <si>
+    <t>sze4sanmat@vasvari.org</t>
+  </si>
+  <si>
+    <t>Kecskés Olivér Zsolt</t>
+  </si>
+  <si>
+    <t>sze4kecoli@vasvari.org</t>
+  </si>
+  <si>
+    <t>sze4dr.pap@vasvari.org</t>
+  </si>
+  <si>
+    <t>Kondacs Pál</t>
+  </si>
+  <si>
+    <t>sze4konpal@vasvari.org</t>
+  </si>
+  <si>
+    <t>Szalontai Péter</t>
+  </si>
+  <si>
+    <t>sze4szapet@vasvari.org</t>
+  </si>
+  <si>
+    <t>Illés Regina</t>
+  </si>
+  <si>
+    <t>sze4illreg@vasvari.org</t>
+  </si>
+  <si>
+    <t>Lengyel Tamás András</t>
+  </si>
+  <si>
+    <t>sze4lentam@vasvari.org</t>
+  </si>
+  <si>
+    <t>Tokaji Ticián</t>
+  </si>
+  <si>
+    <t>tokaji.tician@vasvari.org</t>
+  </si>
+  <si>
+    <t>Füle Zsolt</t>
+  </si>
+  <si>
+    <t>sze4fulzso@vasvari.org</t>
+  </si>
+  <si>
+    <t>Pap Attila Sándor</t>
+  </si>
+  <si>
+    <t>sze4papatt@vasvari.org</t>
+  </si>
+  <si>
+    <t>Dr. Pap Sándor</t>
   </si>
 </sst>
 </file>
@@ -181,8 +229,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normál" xfId="0" builtinId="0"/>
@@ -497,54 +548,54 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10F5D9B8-A17E-42A9-8111-FA53D8520DA1}">
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="19.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.1796875" customWidth="1"/>
     <col min="3" max="3" width="23.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>39</v>
+        <v>3</v>
       </c>
       <c r="B1" t="s">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c r="D1" t="s">
-        <v>38</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C2" t="s">
-        <v>15</v>
+      <c r="B2" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>33</v>
       </c>
       <c r="D2">
         <f ca="1">RANDBETWEEN(1,5)</f>
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" t="s">
-        <v>5</v>
+      <c r="B3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>17</v>
       </c>
       <c r="D3">
-        <f t="shared" ref="D3:D19" ca="1" si="0">RANDBETWEEN(1,5)</f>
+        <f ca="1">RANDBETWEEN(1,5)</f>
         <v>2</v>
       </c>
     </row>
@@ -552,14 +603,14 @@
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C4" t="s">
-        <v>33</v>
+      <c r="B4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>7</v>
       </c>
       <c r="D4">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">RANDBETWEEN(1,5)</f>
         <v>2</v>
       </c>
     </row>
@@ -567,59 +618,59 @@
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" t="s">
-        <v>30</v>
-      </c>
-      <c r="C5" t="s">
-        <v>31</v>
+      <c r="B5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>13</v>
       </c>
       <c r="D5">
-        <f t="shared" ca="1" si="0"/>
-        <v>3</v>
+        <f ca="1">RANDBETWEEN(1,5)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C6" t="s">
-        <v>29</v>
+      <c r="B6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="D6">
-        <f t="shared" ca="1" si="0"/>
-        <v>4</v>
+        <f ca="1">RANDBETWEEN(1,5)</f>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7" t="s">
-        <v>18</v>
-      </c>
-      <c r="C7" t="s">
-        <v>19</v>
+      <c r="B7" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>21</v>
       </c>
       <c r="D7">
-        <f t="shared" ca="1" si="0"/>
-        <v>4</v>
+        <f ca="1">RANDBETWEEN(1,5)</f>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8" t="s">
-        <v>24</v>
-      </c>
-      <c r="C8" t="s">
-        <v>25</v>
+      <c r="B8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>9</v>
       </c>
       <c r="D8">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">RANDBETWEEN(1,5)</f>
         <v>3</v>
       </c>
     </row>
@@ -627,149 +678,149 @@
       <c r="A9">
         <v>8</v>
       </c>
-      <c r="B9" t="s">
-        <v>16</v>
-      </c>
-      <c r="C9" t="s">
-        <v>17</v>
+      <c r="B9" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>52</v>
       </c>
       <c r="D9">
-        <f t="shared" ca="1" si="0"/>
-        <v>3</v>
+        <f ca="1">RANDBETWEEN(1,5)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>9</v>
       </c>
-      <c r="B10" t="s">
-        <v>20</v>
-      </c>
-      <c r="C10" t="s">
-        <v>21</v>
+      <c r="B10" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>46</v>
       </c>
       <c r="D10">
-        <f t="shared" ca="1" si="0"/>
-        <v>5</v>
+        <f ca="1">RANDBETWEEN(1,5)</f>
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>10</v>
       </c>
-      <c r="B11" t="s">
-        <v>26</v>
-      </c>
-      <c r="C11" t="s">
-        <v>27</v>
+      <c r="B11" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="D11">
-        <f t="shared" ca="1" si="0"/>
-        <v>5</v>
+        <f ca="1">RANDBETWEEN(1,5)</f>
+        <v>4</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>11</v>
       </c>
-      <c r="B12" t="s">
-        <v>6</v>
-      </c>
-      <c r="C12" t="s">
-        <v>7</v>
+      <c r="B12" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>39</v>
       </c>
       <c r="D12">
-        <f t="shared" ca="1" si="0"/>
-        <v>3</v>
+        <f ca="1">RANDBETWEEN(1,5)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>12</v>
       </c>
-      <c r="B13" t="s">
-        <v>2</v>
-      </c>
-      <c r="C13" t="s">
-        <v>3</v>
+      <c r="B13" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>15</v>
       </c>
       <c r="D13">
-        <f t="shared" ca="1" si="0"/>
-        <v>3</v>
+        <f ca="1">RANDBETWEEN(1,5)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>13</v>
       </c>
-      <c r="B14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C14" t="s">
-        <v>11</v>
+      <c r="B14" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>35</v>
       </c>
       <c r="D14">
-        <f t="shared" ca="1" si="0"/>
-        <v>3</v>
+        <f ca="1">RANDBETWEEN(1,5)</f>
+        <v>4</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>14</v>
       </c>
-      <c r="B15" t="s">
-        <v>22</v>
-      </c>
-      <c r="C15" t="s">
-        <v>23</v>
+      <c r="B15" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="D15">
-        <f t="shared" ca="1" si="0"/>
-        <v>1</v>
+        <f ca="1">RANDBETWEEN(1,5)</f>
+        <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>15</v>
       </c>
-      <c r="B16" t="s">
-        <v>0</v>
-      </c>
-      <c r="C16" t="s">
-        <v>1</v>
+      <c r="B16" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>29</v>
       </c>
       <c r="D16">
-        <f t="shared" ca="1" si="0"/>
-        <v>4</v>
+        <f ca="1">RANDBETWEEN(1,5)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>16</v>
       </c>
-      <c r="B17" t="s">
-        <v>34</v>
-      </c>
-      <c r="C17" t="s">
-        <v>35</v>
+      <c r="B17" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>25</v>
       </c>
       <c r="D17">
-        <f t="shared" ca="1" si="0"/>
-        <v>2</v>
+        <f ca="1">RANDBETWEEN(1,5)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>17</v>
       </c>
-      <c r="B18" t="s">
-        <v>12</v>
-      </c>
-      <c r="C18" t="s">
-        <v>13</v>
+      <c r="B18" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>48</v>
       </c>
       <c r="D18">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">RANDBETWEEN(1,5)</f>
         <v>5</v>
       </c>
     </row>
@@ -777,20 +828,140 @@
       <c r="A19">
         <v>18</v>
       </c>
-      <c r="B19" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" t="s">
-        <v>9</v>
+      <c r="B19" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>54</v>
       </c>
       <c r="D19">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">RANDBETWEEN(1,5)</f>
         <v>1</v>
       </c>
     </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D20">
+        <f ca="1">RANDBETWEEN(1,5)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D21">
+        <f ca="1">RANDBETWEEN(1,5)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D22">
+        <f ca="1">RANDBETWEEN(1,5)</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D23">
+        <f ca="1">RANDBETWEEN(1,5)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D24">
+        <f ca="1">RANDBETWEEN(1,5)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D25">
+        <f ca="1">RANDBETWEEN(1,5)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D26">
+        <f ca="1">RANDBETWEEN(1,5)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D27">
+        <f ca="1">RANDBETWEEN(1,5)</f>
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
-  <sortState ref="B2:C19">
-    <sortCondition ref="B2:B19"/>
+  <sortState ref="A2:D27">
+    <sortCondition ref="B1"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
